--- a/www/download/COUNTRY.GBR.EXI382.xlsx
+++ b/www/download/COUNTRY.GBR.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34138527607362</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34096134969325</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>35.429</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>26.461</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>27.202</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>27.729</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>28.076</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>27.912</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>28.361</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>27.369</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>28.893</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>29.182</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>29.394</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>29.816</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>30.071</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>30.264</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>29.253</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>28.687</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>28.691</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>28.819</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>29.101</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>28.907</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>31.543</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>36.371</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>32.381</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>31.349</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>32.839</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>34.304</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>34.621</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>29.418</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>22.885</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>24.152</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>24.591</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.908</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>24.048</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>25.357</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>25.461</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>25.565</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>25.966</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>26.108</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>26.233</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.332</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.777</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24.659</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>24.823</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.619</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>26.749</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>30.816</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>27.325</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>26.391</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>27.638</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>29.006</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>64338.853</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>51110.523</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>52469.462</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>53126.984</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>53682.609</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>53182.798</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>53711.414</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>51806.621</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>54643.964</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>54670.285</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>54997.096</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>56155.65</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>56617.615</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>57091.34</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>54503.353</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>53203.327</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>53017.461</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>53294.088</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>54076.166</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>53579.534</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>58359.739</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>67201.087</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>59658.557</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>57601.589</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>60309.588</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>62861.23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>63334.933</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>53093.213</t>
+          <t>92422479054.8985</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35062.833</t>
+          <t>60708700808.3595</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36857.662</t>
+          <t>63338322656.4841</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37485.382</t>
+          <t>63002567819.4781</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>38745.291</t>
+          <t>64530940133.6958</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>38228.534</t>
+          <t>64393916055.8921</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>39187.488</t>
+          <t>62439981535.744</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>37377.664</t>
+          <t>64627274958.7291</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39840.172</t>
+          <t>63045848250.3366</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>39444.429</t>
+          <t>73760356588.6033</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>39186.602</t>
+          <t>75016145599.493</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>40482.728</t>
+          <t>70183780303.7178</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>40438.905</t>
+          <t>63817067878.5147</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>40909.13</t>
+          <t>66665492861.3724</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>38821.163</t>
+          <t>63641617702.0334</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>37710.491</t>
+          <t>60440569238.7562</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>37225.327</t>
+          <t>60903407733.8267</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>37362.742</t>
+          <t>65493728355.0099</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>37472.16</t>
+          <t>65779760844.2134</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>45302.259</t>
+          <t>58861953449.8094</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>49118.627</t>
+          <t>60305516867.0454</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>56528.594</t>
+          <t>66764614788.4058</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>49986.636</t>
+          <t>58620512928.0061</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>48155.831</t>
+          <t>58987520674.8422</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>50425.512</t>
+          <t>60507550710.2616</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>52434.268</t>
+          <t>63456620623.8165</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>52741.382</t>
+          <t>65439223642.255</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>41595798093.9035</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>34938272763.761</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>33351088863.6584</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>36591701295.384</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>41747982875.4389</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>45111359097.5004</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>43350517174.6523</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>45816035830.3721</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>46747816708.3284</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>52144664154.4622</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>50155428808.4697</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>52754987228.5081</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>44344761823.4296</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>46329237565.7157</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>41913181085.4231</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>42087843273.158</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>38877622167.3326</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37523781983.744</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>36488592417.3741</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>41385703494.1755</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>43381632791.4176</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>41719101862.1539</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>37127839188.5148</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>40340959979.1045</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>40885563934.3277</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>43322329035.7704</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>45935738384.2046</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25682264.6376521</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20729971.6844633</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>16973577.1620957</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>15984225.355483</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15194793.2789023</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13632735.8723146</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9012519.37339061</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14004472.6567666</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8761990.82705406</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5102640.25885415</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4672966.0570908</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4201468.76303361</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3719298.63136811</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4630743.77978502</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6376582.56468257</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>8273354.75092087</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>8186516.22048013</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7850852.73559484</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7849030.20523284</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>8713176.87053667</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>8895765.6946221</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9252167.93085556</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>8521635.5893995</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7997281.09709469</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8021582.98660348</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7980977.21774866</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>8173760.55801963</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>129085.958026159</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>208493.700726841</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>238696.626114185</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>245049.35769055</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>261270.869144239</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>306932.521672585</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>308833.139077722</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>302435.501864366</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>277545.99815774</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>269128.839278828</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>290035.486879555</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>317161.230449966</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>332514.410858881</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>335359.45726286</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>325091.992232134</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>362087.514703487</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>376669.977506712</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>418228.416470916</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>411685.703364341</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>423420.137178346</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>521326.475573749</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>550665.768780939</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>513568.436669203</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>486200.95147889</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>543734.695600009</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>538827.676604103</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>534939.906420099</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>344514.277062392</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>461329.814551306</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>524227.482612347</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>536085.133739987</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>579184.214421584</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>690870.313934445</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>672650.403628068</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>674879.153929506</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>604785.049979185</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>691460.69393058</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>753895.142834668</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>754497.388316684</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>710788.895657323</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>746087.498591933</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>713750.231630189</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>781699.624611905</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>820022.408635687</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>973325.161968798</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>954923.42316854</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>884473.771005836</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1023634.71658885</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1032944.58296572</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>958861.04385044</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>938400.300291051</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1025595.16311292</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1023203.55183819</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1035946.11069176</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.276408083930474</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.00356515151932557</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.1051411889632</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.0244230432853727</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.071924238457169</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.152574101849482</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.0960318225934457</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.184179440177033</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.147764006850421</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.243557713150453</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.218696700816553</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.232627470372444</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.0880793280385641</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.116991080589742</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.0737719735260904</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.104005145731891</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.0424999029059656</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.00429167784335904</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.0269554816304056</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.0946354781411511</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.132244776738823</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.354981081283401</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.346338408044219</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.193720490476523</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.233332922308418</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.21032891603678</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.148155745852299</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1413.96527610409</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1526.70879512343</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1408.39557367166</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1515.07766721943</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1697.68667832806</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1847.28930838281</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1740.4254526516</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1905.16734365378</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1843.57898609611</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2048.02105787088</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1961.89404213836</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2031.69480199064</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1698.4928863014</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1766.03341398295</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1654.55475625399</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1698.65211860749</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1576.58427079905</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1518.59123513726</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1469.93318444314</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1681.06480471248</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1621.78251478507</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1353.83040606424</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1358.75604264282</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1528.58914925493</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1479.33083903472</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1504.24323639395</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1583.67265016823</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>54275859807.6825</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>38668464573.056</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>38292044475.5818</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>38315875821.5193</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>39767938376.3468</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>40313886998.2118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>41287378256.9777</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>38774026492.6328</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>38987097336.9918</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.147</t>
+          <t>47037167607.8975</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>46395178026.4035</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>48920588210.7211</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>38034880379.9986</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>40933043716.0792</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>36394428345.6383</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>37615475803.1524</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>39590423478.6341</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>40886644874.6933</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>37421455366.3836</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>39027523041.2562</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>38462004659.9707</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>36142108361.4749</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>33237644572.9578</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>35656020514.7482</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>34390001873.7889</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>36438254003.987</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>39390970804.1538</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>66656192471.3831</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>37297695261.6245</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>36872841026.6358</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>37218019526.5279</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>39118278742.7564</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>40226658606.5973</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40776614430.2136</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>37127126622.319</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>38257206367.2924</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>44911718282.3579</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>44988521873.9083</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>45102036555.0538</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>34410378597.7995</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>36831268074.9614</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>31158725841.3415</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>32638050368.14</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>32419814452.5025</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>34404864465.8071</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>31679614290.3141</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>33245894801.5823</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>31069003833.5618</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>28307729155.3337</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>33204286710.1285</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>35020680876.059</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>33445092310.9156</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>36098193713.1982</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>32154984467.2425</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-12380332663.7006</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1370769311.43155</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1419203448.94597</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1097856294.99143</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>649659633.590385</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>87228391.6144689</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>510763826.764075</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1646899870.31375</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>729890969.699431</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2125449325.53961</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1406656152.49525</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3818551655.66734</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3624501782.19913</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4101775641.1178</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5235702504.29679</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>4977425435.01233</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7170609026.13155</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>6481780408.88621</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>5741841076.06951</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>5781628239.67393</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>7393000826.40886</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7834379206.1412</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>33357862.8292544</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>635339638.68914</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>944909562.873331</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>340060290.788886</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>7235986336.91134</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>1804.79670881625</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>1532.15174330393</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>1556.475958818</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1552.08047466663</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>1575.58185685043</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>1565.44080130015</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.197</t>
+          <t>1573.28922434544</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>1554.27468885606</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>1571.16436816531</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.378</t>
+          <t>1549.20973253188</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>1532.83428777105</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.774</t>
+          <t>1559.06677963471</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.966</t>
+          <t>1548.89077419769</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.523</t>
+          <t>1559.42325652349</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.089</t>
+          <t>1532.49498657815</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1521.98355746393</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>1509.57959236701</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.775</t>
+          <t>1512.0739307803</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.762</t>
+          <t>1509.55594139432</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>1840.1531762927</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4.723</t>
+          <t>1836.25478137175</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.225</t>
+          <t>1834.41458748327</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4.145</t>
+          <t>1829.3454473722</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>1824.70818898568</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>4.561</t>
+          <t>1824.50742676765</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>4.625</t>
+          <t>1820.62908576035</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>1818.30285283979</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>1816.00416917427</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>1931.54892690716</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1928.85414522238</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1915.95653600792</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>1912.02576550307</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1905.36030839543</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1893.834322948</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1892.90801935101</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1891.21996296771</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.147</t>
+          <t>1873.4313050209</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1871.01227108657</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1883.40656023552</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1882.77909501699</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1886.4688933242</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>1863.1522939293</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1854.58220479283</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1847.89708860382</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1849.26916270546</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1858.23640587267</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1853.53368772393</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1850.14414881723</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1847.65876117367</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1842.3656249664</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1837.40340531561</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>1836.52811997552</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>1832.47119629254</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1829.37450440724</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>294778.543862005</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>321437.857673487</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>396868.124199854</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>398894.963704507</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>428094.577537996</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>514551.260646574</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>517912.548243084</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>504209.374305276</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>474243.453476857</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>509314.739012628</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>553904.327195927</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>654103.173994088</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>627362.943683457</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>632091.188619888</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>539962.494697279</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>633453.694816714</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>690007.148895557</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>737134.726509196</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>725010.528169921</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>755493.225697176</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>854398.245309153</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>819771.671136241</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>846327.134500603</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>897141.244876828</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>949526.650085428</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>951134.463696974</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>969144.460485657</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>17077202528.179</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10690878654.4657</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12324786626.0332</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>11886157295.8609</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>12330345340.3866</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12828409224.944</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12059799404.7345</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12015879962.4427</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>11391406720.2789</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>13296224316.248</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>14152433122.4309</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14199337045.0248</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>11634212900.2768</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>13904957030.9438</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>11848781347.9198</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>11522886317.4342</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>12615005680.1593</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13548388058.527</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>14087502186.7492</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>11591182225.1709</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>10795595476.7497</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>12968189531.2146</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>12424318595.0889</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12466259501.6715</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>13073411050.931</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13455394411.8578</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>13191049153.9504</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>291122.055451567</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>318986.838092689</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>388829.648856445</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>411929.621545581</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>457694.723445243</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>556450.237354501</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>572395.288827576</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>570386.140344303</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>527316.436181972</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>574376.53983599</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>618802.259209707</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>713986.562934665</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>687702.612432481</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>688801.420989378</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>576296.112242411</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>680901.845746133</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>713850.03520624</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>771212.187317763</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>763511.492655084</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>802366.926575599</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>905319.270894772</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>877389.781264249</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>890865.423854548</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>934799.277697531</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>995003.362860114</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1004244.37888183</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1025276.565524</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>64338.853</t>
+          <t>69281565706.1953</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51110.523</t>
+          <t>48861447892.2664</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>52469.462</t>
+          <t>49112127252.4213</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>53126.984</t>
+          <t>52657740763.2763</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53682.609</t>
+          <t>57528249711.0724</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>53182.798</t>
+          <t>59642527703.1946</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53711.414</t>
+          <t>62134098957.0545</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>51806.621</t>
+          <t>61863499693.4094</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>54643.964</t>
+          <t>59394418014.1795</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>54670.285</t>
+          <t>72265065274.585</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>54997.096</t>
+          <t>71401828199.0857</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>56155.65</t>
+          <t>72030076473.6688</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56617.615</t>
+          <t>57162218403.182</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57091.34</t>
+          <t>62609534097.935</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>54503.353</t>
+          <t>53591206089.8584</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>53203.327</t>
+          <t>54988814803.912</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>53017.461</t>
+          <t>54954889602.4082</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>53294.088</t>
+          <t>58150540453.1033</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>54076.166</t>
+          <t>55919379975.4494</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>53579.534</t>
+          <t>55601665249.7739</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>58359.739</t>
+          <t>54179875137.6755</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>67201.087</t>
+          <t>55221074818.3379</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>59658.557</t>
+          <t>49952013991.7096</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>57601.589</t>
+          <t>51865100832.8409</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>60309.588</t>
+          <t>51613954537.5099</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>62861.23</t>
+          <t>55047505031.8174</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>63334.933</t>
+          <t>58051255765.5012</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>53093.213</t>
+          <t>3656.4884104379</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35062.833</t>
+          <t>2451.01958079751</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36857.662</t>
+          <t>8038.47534340863</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>37485.382</t>
+          <t>-13034.6578410742</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>38745.291</t>
+          <t>-29600.1459072468</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>38228.534</t>
+          <t>-41898.9767079267</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>39187.488</t>
+          <t>-54482.7405844914</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>37377.664</t>
+          <t>-66176.7660390267</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>39840.172</t>
+          <t>-53072.9827051153</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>39444.429</t>
+          <t>-65061.8008233621</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>39186.602</t>
+          <t>-64897.9320137798</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>40482.728</t>
+          <t>-59883.3889405772</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>40438.905</t>
+          <t>-60339.6687490236</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>40909.13</t>
+          <t>-56710.23236949</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>38821.163</t>
+          <t>-36333.6175451319</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>37710.491</t>
+          <t>-47448.1509294197</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>37225.327</t>
+          <t>-23842.8863106828</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37362.742</t>
+          <t>-34077.4608085673</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>37472.16</t>
+          <t>-38500.9644851632</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>45302.259</t>
+          <t>-46873.7008784231</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>49118.627</t>
+          <t>-50921.0255856186</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>56528.594</t>
+          <t>-57618.1101280078</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>49986.636</t>
+          <t>-44538.2893539452</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>48155.831</t>
+          <t>-37658.0328207033</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>50425.512</t>
+          <t>-45476.7127746859</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>52434.268</t>
+          <t>-53109.9151848552</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>52741.382</t>
+          <t>-56132.1050383476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>83228.432</t>
+          <t>-52204363178.0164</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>57558.766</t>
+          <t>-38170569237.8008</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60193.547</t>
+          <t>-36787340626.3882</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>59608.302</t>
+          <t>-40771583467.4153</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60762.809</t>
+          <t>-45197904370.6858</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>60326.032</t>
+          <t>-46814118478.2506</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>58912.199</t>
+          <t>-50074299552.32</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>60519.997</t>
+          <t>-49847619730.9666</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>59544.505</t>
+          <t>-48003011293.9006</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>68264.366</t>
+          <t>-58968840958.337</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>69533.071</t>
+          <t>-57249395076.6549</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>65656.076</t>
+          <t>-57830739428.644</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>60667.395</t>
+          <t>-45528005502.9052</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>63057.942</t>
+          <t>-48704577066.9912</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>60291.25</t>
+          <t>-41742424741.9387</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>57265.212</t>
+          <t>-43465928486.4778</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>57572.25</t>
+          <t>-42339883922.2489</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>61260.535</t>
+          <t>-44602152394.5763</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>61768.593</t>
+          <t>-41831877788.7002</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>55852.219</t>
+          <t>-44010483024.603</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>57553.201</t>
+          <t>-43384279660.9258</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>64098.029</t>
+          <t>-42252885287.1233</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>56341.173</t>
+          <t>-37527695396.6207</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>56334.691</t>
+          <t>-39398841331.1695</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>58011.273</t>
+          <t>-38540543486.5789</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>60657.36</t>
+          <t>-41592110619.9596</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>62328.425</t>
+          <t>-44860206611.5508</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>468043.712816142</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>507165.927257567</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>625185.868813135</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>683599.90854326</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>744613.551970647</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>854359.845377763</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>899366.556071203</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>886969.273156178</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>844487.95951734</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>880421.106606379</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>903264.692656874</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>950365.798053104</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>981398.408184368</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>878010.74455261</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>789378.476152253</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>856046.9344199</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>867873.877569669</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>933957.142547543</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>938105.77089317</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>1033483.07817383</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>1199475.35024865</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>1075374.39920145</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>1074728.52096841</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>1096300.49398911</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1139727.03109913</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1158956.91238749</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1170049.46423359</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>34629.753</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>27436.73</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>28839.854</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>28799.043</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>29110.004</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>28608.245</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>28667.991</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>28961.603</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>28932.797</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>28708.847</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>28859.908</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>29502.52</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>29854.286</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>29965.525</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>28986.863</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>27996.4</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>27975.437</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>28142.022</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>28358.91</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>28178.717</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>30712.97</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>35592.411</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>31397.297</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>30562.425</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>32078.988</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>33416.795</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>33791.383</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>775792.940825431</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>833705.815963904</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1027506.22851103</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>1119909.10133354</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1226237.2592844</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>1413617.31918309</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>1433118.18118687</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>1483845.79074451</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1425844.04212145</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1520956.86474657</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1598837.06685805</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>1678416.45976675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1752719.9410312</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>1541576.81568826</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>1395148.53574731</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>1494009.20163338</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1514196.76652146</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1650501.03010506</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1648960.06174615</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1816951.91548278</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>2104058.33366382</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1901432.99988731</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>1864809.94132948</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1930121.9692226</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>2017101.67207394</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2048283.47099292</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>2075347.60032388</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>34968.251</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>29985.484</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>28833.982</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>31367.38</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>35365.156</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>38357.804</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>37091.919</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>38847.786</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>39892.458</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>44320.376</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>43076.897</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>44931.181</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>38341.614</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>39713.778</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>36103.425</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>36092.031</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>33265.241</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>31610.09</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>31129.257</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>35403.837</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>37079.523</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>35907.765</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>32059.612</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>34380.379</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>34878.465</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>36781.798</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>38761.8</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>51.83</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>27.83</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5.65</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-9.03</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-9.9</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>5.47</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>57.43</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>44.57</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>36.07</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>32.429</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>26.733</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>20.519</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>19.414</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>17.162</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11.285</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>17.941</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>11.063</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.075</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5.611</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.538</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>5.623</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>7.998</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>10.389</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>9.932</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>9.967</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>11.168</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>11.655</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>11.996</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>11.068</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10.414</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>10.464</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10.404</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>10.636</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>507727.535983255</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>558858.561375514</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>689637.298193556</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>721031.388994151</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>746524.069115517</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>827523.669885274</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>844526.80070519</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>867675.533428481</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>840456.929518083</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>906594.759290409</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>957924.692952047</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1028231.29615113</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1081721.55383048</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>955855.468385235</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>779435.696993254</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>846449.453057537</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>874973.596857371</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>982581.415954029</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>974144.407305182</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1068321.6002729</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1198946.24664199</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1146961.24685864</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1083553.01193116</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1094144.43522897</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1139110.07773071</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1153440.20302353</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1174253.71862267</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>53093212944.5983</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>35062832999.9873</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>36857662000.0008</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>37485382000.0066</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>38745291000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>38228533999.9899</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>39187488000.002</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>37377664000.0033</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>39840171999.9967</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>39444429000.003</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>39186602000.0179</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>40482728000.0097</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>40438904999.9918</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>40909130000.0037</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>38821162999.995</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>37710490999.9922</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>37225327000.0061</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>37362742000.0054</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>37472160000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>45302259332.5548</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>49118627134.4842</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>56528593751.3536</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>49986635907.1867</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>48155830532.5504</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>50425512047.352</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>52434267542.0527</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>52741381965.7925</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>64338853334.664</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>51110522999.9962</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>52469461999.9964</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>53126984000.0053</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>53682609000.0004</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>53182797999.9932</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>53711414000.0004</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>51806621000.0002</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>54643963999.9988</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>54670284999.9993</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>54997096000.012</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>56155650000.0008</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>56617614999.9909</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>57091339999.9999</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>54503352999.9986</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>53203326999.9902</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>53017460999.9973</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>53294088000.0026</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>54076166000.0024</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>53579534032.4765</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>58359739451.5685</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>67201087170.9512</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>59658556993.1228</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>57601588846.2819</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>60309587862.6613</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>62861230107.6549</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>63334932694.5987</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>34629752803.5204</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27436730292.7606</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>28839853733.907</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>28799042923.1088</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>29110004029.1382</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>28608244755.5897</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>28667990679.3029</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>28961603306.9992</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>28932796673.6997</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>28708846833.5645</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>28859907799.6023</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>29502519774.6798</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>29854285650.7932</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>29965524883.2669</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>28986863150.1188</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>27996400169.4264</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>27975436987.5695</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>28142022182.2748</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>28358909681.3981</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>28178717358.6397</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>30712970219.2171</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>35592410799.2934</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>31397297214.5051</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>30562424871.9803</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>32078987743.1626</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>33416795118.0902</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>33791383364.5422</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>35428802.6573851</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>26460899.9999992</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27202399.9999995</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>27728700.0000013</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>28076300.0000035</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>27912199.9999991</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>28361200.000004</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>27368799.9999928</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>28893499.9999954</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>29181900.0000053</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>29394300.0000065</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>29816000.0000098</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>30071300.0000035</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>30263599.9999966</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>29253299.9999982</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>28687499.9999978</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>28690699.9999955</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>28818999.9999968</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>29100799.9999908</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>28906695.5660623</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>31543347.3056017</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>36370940.6645325</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>32381497.0191983</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>31349451.4485172</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>32838913.3859083</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>34304075.4118459</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>34621086.3560279</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>29417835.6405701</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22884699.9999999</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23680199.9999991</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>24151700.0000004</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>24591100.0000034</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>24420299.9999998</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>24908000.0000036</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24048299.999991</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>25357099.999995</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>25461000.0000057</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>25564800.0000056</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>25966000.0000094</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>26108300.0000041</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>26233499.9999966</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>25331999.9999982</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24777199.9999979</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>24659399.9999941</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>24709599.9999976</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>24823299.999991</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>24618743.6547123</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>26749352.8854372</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>30815604.1371804</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>27324875.1234989</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>26390976.2795109</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>27637877.1100358</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>28800082.3188842</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>29005829.1903475</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>64338853334.664</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>51110522999.9962</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>52469461999.9964</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>53126984000.0053</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>53682609000.0004</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>53182797999.9932</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>53711414000.0004</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>51806621000.0002</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>54643963999.9988</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>54670284999.9993</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>54997096000.012</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>56155650000.0008</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>56617614999.9909</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>57091339999.9999</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>54503352999.9986</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>53203326999.9902</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>53017460999.9973</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>53294088000.0026</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>54076166000.0024</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>53579534032.4765</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>58359739451.5685</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>67201087170.9512</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>59658556993.1228</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>57601588846.2819</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>60309587862.6613</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>62861230107.6549</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>63334932694.5987</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>53093212944.5983</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>35062832999.9873</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>36857662000.0008</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>37485382000.0066</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>38745291000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>38228533999.9899</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>39187488000.002</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>37377664000.0033</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>39840171999.9967</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>39444429000.003</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>39186602000.0179</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>40482728000.0097</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>40438904999.9918</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>40909130000.0037</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>38821162999.995</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>37710490999.9922</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>37225327000.0061</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>37362742000.0054</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>37472160000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>45302259332.5548</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>49118627134.4842</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>56528593751.3536</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>49986635907.1867</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>48155830532.5504</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>50425512047.352</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>52434267542.0527</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>52741381965.7925</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2336726.93700647</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2541754.62214784</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3128455.3268015</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3358749.50820294</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3594104.42255234</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4136231.96335184</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4244960.52320715</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>4354969.70035026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4207035.28053769</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4483932.61328351</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4689807.02771247</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5009592.37599267</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5265033.89995199</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4677685.59888742</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4101431.35083591</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>4487486.5713447</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4600240.85949706</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>5013018.67513661</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4994869.25201331</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>5449915.49955852</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>6271029.50573667</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5609089.73128654</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>5502301.10050306</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>5804244.09140028</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>6055990.71042409</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>6141249.86940272</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>6200895.21132567</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>854976.28285482</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>921792.484952967</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1134973.78659673</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1235026.27145142</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1349245.93179492</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1556478.96924398</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1584937.24995105</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1631787.51002303</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1566811.6349297</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1667883.60475486</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1744795.63185621</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1833188.23980859</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1914900.24168434</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1681836.83574906</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1516898.94643804</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1638995.29677145</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1662286.85746881</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1812298.70286409</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1808827.6413501</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1995992.58596611</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2310675.40907422</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2083356.15020749</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2045466.9596099</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2118468.01160666</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2213342.20548565</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>2247451.69981159</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2279101.58595894</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
